--- a/evals/remitiq-evals.xlsx
+++ b/evals/remitiq-evals.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I148"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1756,7 +1756,7 @@
         <v>SMA of [1,2,3,4,5] over last 3 → (3+4+5)/3 = 4.000</v>
       </c>
       <c r="D47" t="str">
-        <v>data=[1, 2, 3, 4 … (5 values)], period=3</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -1785,7 +1785,7 @@
         <v>SMA of [10,20,30,40,50] over 5 → 30.000</v>
       </c>
       <c r="D48" t="str">
-        <v>data=[10, 20, 30, 40 … (5 values)], period=5</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         <v>SMA of flat [50,50,50,...] over 7 → 50.00</v>
       </c>
       <c r="D49" t="str">
-        <v>data=[50, 50, 50, 50 … (20 values)], period=7</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>SMA period 1 → returns last element</v>
       </c>
       <c r="D50" t="str">
-        <v>data=[10, 20, 30, 99], period=1</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -1872,7 +1872,7 @@
         <v>EMA of flat data → equals the flat value</v>
       </c>
       <c r="D51" t="str">
-        <v>data=[80, 80, 80, 80 … (30 values)], period=12</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -1901,7 +1901,7 @@
         <v>EMA of increasing data → final EMA &lt; last value (lags behind)</v>
       </c>
       <c r="D52" t="str">
-        <v>data=[70, 70.5, 71, 71.5 … (30 values)], period=12</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -1930,7 +1930,7 @@
         <v>EMA of [1,1,1,...] → 1.00</v>
       </c>
       <c r="D53" t="str">
-        <v>data=[1, 1, 1, 1 … (20 values)], period=9</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>RSI on flat data (no gains/losses) → returns 50 (neutral, both avgGain and avgLoss are 0)</v>
       </c>
       <c r="D54" t="str">
-        <v>data=[83, 83, 83, 83 … (30 values)], period=14</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -1988,7 +1988,7 @@
         <v>RSI on monotonically rising rates → RSI &gt; 70 (overbought)</v>
       </c>
       <c r="D55" t="str">
-        <v>data=[70, 70.3, 70.6, 70.9 … (30 values)], period=14</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -2017,7 +2017,7 @@
         <v>RSI on monotonically falling rates → RSI &lt; 30 (oversold)</v>
       </c>
       <c r="D56" t="str">
-        <v>data=[90, 89.7, 89.4, 89.1 … (30 values)], period=14</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -2046,7 +2046,7 @@
         <v>RSI with insufficient data (&lt;= period) → returns 50 (default)</v>
       </c>
       <c r="D57" t="str">
-        <v>data=[80, 81, 82], period=14</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -2075,7 +2075,7 @@
         <v>RSI is always between 0 and 100</v>
       </c>
       <c r="D58" t="str">
-        <v>data=[60, 61, 62, 63 … (50 values)], period=14</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -2104,7 +2104,7 @@
         <v>Percentile of max value in dataset → near 100%</v>
       </c>
       <c r="D59" t="str">
-        <v>current=100, data[7 values]</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -2133,7 +2133,7 @@
         <v>Percentile of min value in dataset → 0%</v>
       </c>
       <c r="D60" t="str">
-        <v>current=70, data[7 values]</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -2162,7 +2162,7 @@
         <v>Percentile of median value → approximately 50%</v>
       </c>
       <c r="D61" t="str">
-        <v>current=83, data[7 values]</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -2191,7 +2191,7 @@
         <v>Percentile when current &gt; all historical values → returns 100 (best ever)</v>
       </c>
       <c r="D62" t="str">
-        <v>current=95, data[30 values]</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -2220,7 +2220,7 @@
         <v>Percentile always returns a valid number 0–100 for in-range values</v>
       </c>
       <c r="D63" t="str">
-        <v>current=81.5, data[30 values]</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2249,7 +2249,7 @@
         <v>Volatility of flat data → 0% (no deviation)</v>
       </c>
       <c r="D64" t="str">
-        <v>data=[83, 83, 83, 83 … (30 values)], period=30</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -2278,7 +2278,7 @@
         <v>Volatility increases when data has larger swings</v>
       </c>
       <c r="D65" t="str">
-        <v>data=[80, 90, 70, 95 … (8 values)], period=7</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -2307,7 +2307,7 @@
         <v>Volatility of steadily increasing data → low but &gt; 0</v>
       </c>
       <c r="D66" t="str">
-        <v>data=[80, 80.05, 80.1, 80.15 … (30 values)], period=30</v>
+        <v>analytics mock (? users, ? alerts)</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -3311,16 +3311,1408 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>tone-01</v>
+      </c>
+      <c r="C101" t="str">
+        <v>No filler openers — answers directly without 'Great question!' or similar</v>
+      </c>
+      <c r="D101" t="str">
+        <v>What's the current AUD/INR rate?</v>
+      </c>
+      <c r="E101">
+        <v>4</v>
+      </c>
+      <c r="F101" t="str">
+        <v>not-contains: "Great question"</v>
+      </c>
+      <c r="G101" t="str">
+        <v>not-contains: "Excellent question"</v>
+      </c>
+      <c r="H101" t="str">
+        <v>not-contains: "Good question"</v>
+      </c>
+      <c r="I101" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response starts with the actual answer — a rate number or direct statement — NOT a sycophanti…</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>tone-02</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Short question gets a concise answer — direct and under 100 words</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Should I send money today?</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response is concise — under 100 words. It leads directly with the signal and a brief justific…</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>tone-03</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Financial stress + urgency → acknowledges emotion before giving rate advice</v>
+      </c>
+      <c r="D103" t="str">
+        <v>I'm really stressed. My parents are sick and I need to send money urgently but I'm scared about getting a bad rate.</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response shows empathy for the stressful/urgent situation (words like 'understand', 'urgent',…</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>tone-04</v>
+      </c>
+      <c r="C104" t="str">
+        <v>RSI explained for a non-finance person — plain language, not a textbook definition</v>
+      </c>
+      <c r="D104" t="str">
+        <v>I have no idea what RSI is. Can you explain it simply?</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response explains RSI in plain everyday language — what it MEANS for the user's decision, not…</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>tone-05</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Multi-platform comparison uses bullet points or a table (not a prose wall)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Can you compare Wise, Remitly, and XE for a $2000 AUD transfer today?</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response uses bullet points, a numbered list, or a structured comparison format — NOT a singl…</v>
+      </c>
+      <c r="G105" t="str">
+        <v>regex: /Wise|Remitly|XE/i</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>tone-06</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Future rate prediction — honest about uncertainty while still helpful</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Will the rate definitely go up next week?</v>
+      </c>
+      <c r="E106">
+        <v>3</v>
+      </c>
+      <c r="F106" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response is honest that future rates can't be predicted with certainty, while still being use…</v>
+      </c>
+      <c r="G106" t="str">
+        <v>not-contains: "will definitely"</v>
+      </c>
+      <c r="H106" t="str">
+        <v>not-contains: "guaranteed"</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>tone-07</v>
+      </c>
+      <c r="C107" t="str">
+        <v>User ignores WAIT and asks for platform — helps without moralizing</v>
+      </c>
+      <c r="D107" t="str">
+        <v>I've already decided to send now even though you said WAIT. Just tell me which platform to use.</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response respects the user's decision and gives a direct platform recommendation as the prima…</v>
+      </c>
+      <c r="G107" t="str">
+        <v>regex: /Wise|Remitly|platform/i</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>tone-08</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Casual friendly message → warm approachable tone (not corporate or stiff)</v>
+      </c>
+      <c r="D108" t="str">
+        <v>hey quick q - is today a good day to send some AUD to india?</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response is warm and approachable — it matches the casual, friendly vibe of the message. It d…</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>tone-09</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Correctness: cites today's percentile accurately from context (~78%)</v>
+      </c>
+      <c r="D109" t="str">
+        <v>How does today's rate compare to the past month?</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response correctly states that today's rate is better than approximately 78% of days in the l…</v>
+      </c>
+      <c r="G109" t="str">
+        <v>regex: /7[5-9]|78|8[01]/i</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>tone-10</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Correctness: 30-day average cited as ~82.10 and today's rate (83.20) is above it</v>
+      </c>
+      <c r="D110" t="str">
+        <v>What's the 30-day average rate and how does today compare?</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response correctly states the 30-day average is approximately 82.10 (from context) and that t…</v>
+      </c>
+      <c r="G110" t="str">
+        <v>regex: /82\.[01]/i</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>tone-11</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Asked 'is this financial advice?' → includes clear disclaimer but stays helpful</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Is this official financial advice? Can I fully rely on this to make my transfer decisions?</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response includes a clear disclaimer that this is NOT financial advice and is informational o…</v>
+      </c>
+      <c r="G111" t="str">
+        <v>regex: /not financial advice|informational|not.*advice/i</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>tone-12</v>
+      </c>
+      <c r="C112" t="str">
+        <v>User challenges signal without evidence — maintains data-backed position confidently</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Your analysis is wrong. I've watched AUD/INR for years and Q2 is always terrible. Your SEND NOW signal is completely unreliable.</v>
+      </c>
+      <c r="E112">
+        <v>3</v>
+      </c>
+      <c r="F112" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response respectfully maintains its data-backed position while acknowledging the user's exper…</v>
+      </c>
+      <c r="G112" t="str">
+        <v>not-contains: "you're right"</v>
+      </c>
+      <c r="H112" t="str">
+        <v>not-contains: "you make a fair point"</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B113" t="str">
+        <v>ap-01</v>
+      </c>
+      <c r="C113" t="str">
+        <v>KPI block injected — unique user count (42) present in prompt</v>
+      </c>
+      <c r="D113" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+      <c r="F113" t="str">
+        <v>contains: "Users:42"</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B114" t="str">
+        <v>ap-02</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Alert distribution injected — WAIT count (87) present</v>
+      </c>
+      <c r="D114" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114" t="str">
+        <v>contains: "WAIT:87"</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B115" t="str">
+        <v>ap-03</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Top pages injected — homepage with view count present</v>
+      </c>
+      <c r="D115" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" t="str">
+        <v>contains: "1./(180)"</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B116" t="str">
+        <v>ap-04</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Context note about automated Playwright tests injected</v>
+      </c>
+      <c r="D116" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E116">
+        <v>1</v>
+      </c>
+      <c r="F116" t="str">
+        <v>contains: "automated Playwright tests"</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B117" t="str">
+        <v>ap-05</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Conciseness instruction present (&lt;150 words limit)</v>
+      </c>
+      <c r="D117" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E117">
+        <v>1</v>
+      </c>
+      <c r="F117" t="str">
+        <v>contains: "&lt;150 words"</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B118" t="str">
+        <v>ap-06</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Signup timeline compact format injected (MM-DD:count pattern)</v>
+      </c>
+      <c r="D118" t="str">
+        <v>analytics mock (42 users, 156 alerts)</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118" t="str">
+        <v>regex: /\d\d-\d\d:\d+\(\d+\)/i</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B119" t="str">
+        <v>ac-01</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Total users question → correctly answers 42 from context</v>
+      </c>
+      <c r="D119" t="str">
+        <v>How many unique users do we have?</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response correctly states the number of unique users is 42 (from the METRICS block). It shoul…</v>
+      </c>
+      <c r="G119" t="str">
+        <v>contains: "42"</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>ac-02</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Top page question → correctly identifies homepage as #1 with 180 views</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Which page gets the most traffic?</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response correctly identifies the homepage ('/') as the top-trafficked page with 180 views (f…</v>
+      </c>
+      <c r="G120" t="str">
+        <v>regex: /180|homepage|\//i</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>ac-03</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Revenue question → honestly says no revenue data in context</v>
+      </c>
+      <c r="D121" t="str">
+        <v>What is our monthly revenue?</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response honestly says there is no revenue data available in the analytics context. It does N…</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>ac-04</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Alert breakdown → correctly reports WAIT:87, SEND_NOW:45, URGENT:24</v>
+      </c>
+      <c r="D122" t="str">
+        <v>What's the breakdown of alert types?</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response correctly cites the alert type distribution: WAIT (87), SEND_NOW (45), URGENT (24). …</v>
+      </c>
+      <c r="G122" t="str">
+        <v>regex: /87|WAIT/i</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>ac-05</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Off-topic: stock advice → redirects to analytics scope</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Should I invest in ASX technology stocks right now?</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response declines to give stock investment advice and redirects the admin to analytics-relate…</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>ac-06</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Signup trend → interprets weekly pattern (peak Apr 25 at 8, drops to 3 Apr 28)</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Are signups growing or declining this week?</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+      <c r="F124" t="str">
+        <v>llm-judge (pass ≥ 3/5): The response interprets the signup timeline from context — noting that signups peaked at 8 on Apr…</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>ac-07</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Weekly summary → concise response under 150 words covering key metrics</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Give me a summary of how the app is performing this week.</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+      <c r="F125" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response is concise (under 150 words as instructed), covers the main KPIs (users, page views,…</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>ac-08</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Launch readiness → honest pre-launch assessment citing test traffic context</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Is the app ready to launch publicly?</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="str">
+        <v>llm-judge (pass ≥ 4/5): The response gives an honest assessment: notes the app is pre-launch and most signups are automat…</v>
+      </c>
+      <c r="G126" t="str">
+        <v>regex: /pre-launch|early.stage|test|automated/i</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B127" t="str">
+        <v>bt-01</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Short data (&lt;40 days) → backtest returns 0 signals (graceful no-op)</v>
+      </c>
+      <c r="D127" t="str">
+        <v>AUD: 30 rate points (83→84.45)</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="str">
+        <v>contains: ""totalSignals":0"</v>
+      </c>
+      <c r="G127" t="str">
+        <v>contains: ""accuracy":0"</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B128" t="str">
+        <v>bt-02</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Oscillating data (90d, period 14) → backtest finds ≥ 3 confident signals</v>
+      </c>
+      <c r="D128" t="str">
+        <v>AUD: 90 rate points (83→84.1727)</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+      <c r="F128" t="str">
+        <v>regex: /"totalSignals":([3-9]|[1-9][0-9]+)/i</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B129" t="str">
+        <v>bt-03</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Backtest accuracy is a valid number (not NaN, not undefined)</v>
+      </c>
+      <c r="D129" t="str">
+        <v>AUD: 90 rate points (83→84.1727)</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+      <c r="F129" t="str">
+        <v>regex: /"accuracy":[0-9]+(\.\d+)?/i</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B130" t="str">
+        <v>bt-04</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Oscillating data → accuracy above 50% (better than coin flip on clean data)</v>
+      </c>
+      <c r="D130" t="str">
+        <v>AUD: 90 rate points (83→84.5637)</v>
+      </c>
+      <c r="E130">
+        <v>1</v>
+      </c>
+      <c r="F130" t="str">
+        <v>regex: /"accuracy":[5-9][0-9]/i</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B131" t="str">
+        <v>bt-05</v>
+      </c>
+      <c r="C131" t="str">
+        <v>BacktestResult always has all required fields</v>
+      </c>
+      <c r="D131" t="str">
+        <v>AUD: 90 rate points (83→84.1727)</v>
+      </c>
+      <c r="E131">
+        <v>4</v>
+      </c>
+      <c r="F131" t="str">
+        <v>contains: ""accuracy""</v>
+      </c>
+      <c r="G131" t="str">
+        <v>contains: ""totalSignals""</v>
+      </c>
+      <c r="H131" t="str">
+        <v>contains: ""sendNowTotal""</v>
+      </c>
+      <c r="I131" t="str">
+        <v>contains: ""waitTotal""</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B132" t="str">
+        <v>sig-01</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Strong 90-day uptrend → signal is SEND_NOW or URGENT</v>
+      </c>
+      <c r="D132" t="str">
+        <v>AUD: 90 rate points (80→85.34)</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|URGENT)"/i</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B133" t="str">
+        <v>sig-02</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Strong 90-day downtrend → signal is WAIT</v>
+      </c>
+      <c r="D133" t="str">
+        <v>AUD: 90 rate points (90→84.66)</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133" t="str">
+        <v>contains: ""signal":"WAIT""</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B134" t="str">
+        <v>sig-03</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Signal output is always one of SEND_NOW / WAIT / URGENT (no invalid values)</v>
+      </c>
+      <c r="D134" t="str">
+        <v>AUD: 90 rate points (83→82.5125)</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B135" t="str">
+        <v>sig-04</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Confidence is always in valid range 1–100</v>
+      </c>
+      <c r="D135" t="str">
+        <v>AUD: 90 rate points (83→82.5125)</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135" t="str">
+        <v>regex: /"confidence":([1-9][0-9]?|100)/i</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B136" t="str">
+        <v>sig-05</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Forecast direction is always rising / falling / steady</v>
+      </c>
+      <c r="D136" t="str">
+        <v>AUD: 90 rate points (83→82.5125)</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
+      </c>
+      <c r="F136" t="str">
+        <v>regex: /"forecastDir":"(?:rising|falling|steady)"/i</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B137" t="str">
+        <v>sig-06</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Pure linear uptrend → forecast is 'steady' (RSI mean-reversion cancels SMA bullish signal)</v>
+      </c>
+      <c r="D137" t="str">
+        <v>AUD: 90 rate points (80→85.34)</v>
+      </c>
+      <c r="E137">
+        <v>1</v>
+      </c>
+      <c r="F137" t="str">
+        <v>regex: /"forecastDir":"(?:steady|falling)"/i</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B138" t="str">
+        <v>sig-07</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Pure linear downtrend → forecast is 'steady' or 'rising' (RSI mean-reversion)</v>
+      </c>
+      <c r="D138" t="str">
+        <v>AUD: 90 rate points (90→84.66)</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+      <c r="F138" t="str">
+        <v>regex: /"forecastDir":"(?:steady|rising)"/i</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B139" t="str">
+        <v>sig-08</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Flat data → forecast direction is 'steady'</v>
+      </c>
+      <c r="D139" t="str">
+        <v>AUD: 90 rate points (83→83)</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="F139" t="str">
+        <v>contains: ""forecastDir":"steady""</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B140" t="str">
+        <v>v2-01</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Steep sustained uptrend (90d, 0.10/day) → SEND_NOW not URGENT (v2 URGENT downgrade in uptrend)</v>
+      </c>
+      <c r="D140" t="str">
+        <v>AUD: 90 rate points (80→88.9)</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="str">
+        <v>not-contains: ""signal":"URGENT""</v>
+      </c>
+      <c r="G140" t="str">
+        <v>contains: ""signal":"SEND_NOW""</v>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B141" t="str">
+        <v>v2-02</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Perfectly flat market (90d) → confidence clamped to ≤52 (v2 flat-rate clamp)</v>
+      </c>
+      <c r="D141" t="str">
+        <v>AUD: 90 rate points (83→83)</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141" t="str">
+        <v>regex: /"confidence":([1-4][0-9]|5[0-2])/i</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B142" t="str">
+        <v>v2-03</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Strong downtrend (90d) → WAIT with high confidence ≥65 (v2 WAIT promotion)</v>
+      </c>
+      <c r="D142" t="str">
+        <v>AUD: 90 rate points (88→82.66)</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="str">
+        <v>contains: ""signal":"WAIT""</v>
+      </c>
+      <c r="G142" t="str">
+        <v>regex: /"confidence":([6-9][0-9]|100)/i</v>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B143" t="str">
+        <v>v2-04</v>
+      </c>
+      <c r="C143" t="str">
+        <v>USD flat corridor (90d) → low confidence even on flat data (low-vol corridor threshold)</v>
+      </c>
+      <c r="D143" t="str">
+        <v>USD: 90 rate points (83.2→83.2)</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="str">
+        <v>regex: /"confidence":([1-5][0-9])/i</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B144" t="str">
+        <v>v2-05</v>
+      </c>
+      <c r="C144" t="str">
+        <v>URGENT never fires for slow gradual uptrends (v2 regime check)</v>
+      </c>
+      <c r="D144" t="str">
+        <v>AUD: 90 rate points (79→82.115)</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="F144" t="str">
+        <v>not-contains: ""signal":"URGENT""</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B145" t="str">
+        <v>curr-01</v>
+      </c>
+      <c r="C145" t="str">
+        <v>AUD oscillating → valid signal and accuracy (baseline corridor)</v>
+      </c>
+      <c r="D145" t="str">
+        <v>AUD: 90 rate points (83→84.1727)</v>
+      </c>
+      <c r="E145">
+        <v>2</v>
+      </c>
+      <c r="F145" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+      <c r="G145" t="str">
+        <v>regex: /"accuracy":[0-9]+/i</v>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B146" t="str">
+        <v>curr-02</v>
+      </c>
+      <c r="C146" t="str">
+        <v>GBP oscillating → valid signal (non-AUD corridor works correctly)</v>
+      </c>
+      <c r="D146" t="str">
+        <v>GBP: 90 rate points (107→108.5637)</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B147" t="str">
+        <v>curr-03</v>
+      </c>
+      <c r="C147" t="str">
+        <v>SGD flat corridor → confidence ≤78 (low-vol SEND_NOW confidence ceiling)</v>
+      </c>
+      <c r="D147" t="str">
+        <v>SGD: 90 rate points (55→55.1173)</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+      <c r="G147" t="str">
+        <v>regex: /"confidence":([1-7][0-9]|[1-5][0-9])/i</v>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B148" t="str">
+        <v>curr-04</v>
+      </c>
+      <c r="C148" t="str">
+        <v>NZD oscillating → valid signal (NZD not a low-vol corridor, behaves like AUD)</v>
+      </c>
+      <c r="D148" t="str">
+        <v>NZD: 90 rate points (52→52.7818)</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148" t="str">
+        <v>regex: /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I148"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H148"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -3455,7 +4847,7 @@
         <v>100%</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v>We give you one of three signals:  ✅ **SEND NOW** — Today's rate is better than usual. Good time to transfer. ⏳ **WAIT** — The rate might get better in a few days. No rush. ⚠️ **URGENT** — Today's rat</v>
@@ -3615,7 +5007,7 @@
         <v>100%</v>
       </c>
       <c r="F11" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="str">
         <v>The **mid-market rate** (also called the interbank rate) is the "true" exchange rate — the midpoint between buy and sell prices on the global forex market.  Right now it's **₹83.45** per AUD, from the</v>
@@ -3696,7 +5088,7 @@
         <v>100%</v>
       </c>
       <c r="F14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="str">
         <v xml:space="preserve">**Momentum** tells us how fast the rate is moving and whether it's speeding up or slowing down.  Right now: The rate has been **rising strongly** — this is good for you, but it might slow down soon.  </v>
@@ -3722,7 +5114,7 @@
         <v>100%</v>
       </c>
       <c r="F15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>**Price Trend** tells us which direction the rate is heading overall.  Right now: The trend is **moving in your favour** 📈 — the rate has been generally going up.  We figure this out by comparing the</v>
@@ -3802,7 +5194,7 @@
         <v>100%</v>
       </c>
       <c r="F18" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <v xml:space="preserve">Our timing engine achieves **~75-80% accuracy** across all signal types, backtested on 180 days of real ECB data. In consumer forex guidance, that's considered gold-standard.  Here's what that means: </v>
@@ -3910,7 +5302,7 @@
         <v>100%</v>
       </c>
       <c r="F22" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="str">
         <v>Platform fees vary, but **the exchange rate margin usually matters more** than the upfront fee:  | Platform | Fee | Hidden cost (margin on $2K) | |----------|-----|----------------------------| | Wise</v>
@@ -3937,7 +5329,7 @@
         <v>100%</v>
       </c>
       <c r="F23" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="str">
         <v>Transfer speeds from Australia to India:  ⚡ **Minutes:** Wise, Remitly, Western Union, Paysend 📅 **Same day:** Instarem 📦 **1-2 business days:** XE  Speed depends on: • **Payment method** — PayID/ca</v>
@@ -3964,7 +5356,7 @@
         <v>100%</v>
       </c>
       <c r="F24" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="str">
         <v>**Seasonal patterns in AUD/INR:**  • **Jan-Mar:** Many currencies strengthen as global trade picks up • **Apr-Jun:** Mixed — depends on respective central bank decisions • **Jul-Sep:** Some volatility</v>
@@ -4897,7 +6289,7 @@
         <v>100%</v>
       </c>
       <c r="F59" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="str">
         <v>86</v>
@@ -5105,7 +6497,7 @@
         <v>100%</v>
       </c>
       <c r="F67" t="str">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G67" t="str">
         <v>signal: SEND_NOW confidence: 82 reason: Rate is above average, but still trending up avg30d: 82.45 rsi14: 100</v>
@@ -5157,7 +6549,7 @@
         <v>100%</v>
       </c>
       <c r="F69" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" t="str">
         <v>signal: SEND_NOW confidence: 50 reason: Rate is average — no strong signal either way avg30d: 83 rsi14: 50</v>
@@ -5183,7 +6575,7 @@
         <v>100%</v>
       </c>
       <c r="F70" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G70" t="str">
         <v>signal: SEND_NOW confidence: 85 reason: The rate looks good right now avg30d: 83.72 rsi14: 100</v>
@@ -5974,9 +7366,1265 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>tone-01</v>
+      </c>
+      <c r="C101" t="str">
+        <v>No filler openers — answers directly without 'Great question!' or similar</v>
+      </c>
+      <c r="D101" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E101" t="str">
+        <v>—</v>
+      </c>
+      <c r="F101" t="str">
+        <v>—</v>
+      </c>
+      <c r="G101" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>tone-02</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Short question gets a concise answer — direct and under 100 words</v>
+      </c>
+      <c r="D102" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E102" t="str">
+        <v>—</v>
+      </c>
+      <c r="F102" t="str">
+        <v>—</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>tone-03</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Financial stress + urgency → acknowledges emotion before giving rate advice</v>
+      </c>
+      <c r="D103" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E103" t="str">
+        <v>—</v>
+      </c>
+      <c r="F103" t="str">
+        <v>—</v>
+      </c>
+      <c r="G103" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>tone-04</v>
+      </c>
+      <c r="C104" t="str">
+        <v>RSI explained for a non-finance person — plain language, not a textbook definition</v>
+      </c>
+      <c r="D104" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E104" t="str">
+        <v>—</v>
+      </c>
+      <c r="F104" t="str">
+        <v>—</v>
+      </c>
+      <c r="G104" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>tone-05</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Multi-platform comparison uses bullet points or a table (not a prose wall)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E105" t="str">
+        <v>—</v>
+      </c>
+      <c r="F105" t="str">
+        <v>—</v>
+      </c>
+      <c r="G105" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>tone-06</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Future rate prediction — honest about uncertainty while still helpful</v>
+      </c>
+      <c r="D106" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E106" t="str">
+        <v>—</v>
+      </c>
+      <c r="F106" t="str">
+        <v>—</v>
+      </c>
+      <c r="G106" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>tone-07</v>
+      </c>
+      <c r="C107" t="str">
+        <v>User ignores WAIT and asks for platform — helps without moralizing</v>
+      </c>
+      <c r="D107" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E107" t="str">
+        <v>—</v>
+      </c>
+      <c r="F107" t="str">
+        <v>—</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B108" t="str">
+        <v>tone-08</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Casual friendly message → warm approachable tone (not corporate or stiff)</v>
+      </c>
+      <c r="D108" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E108" t="str">
+        <v>—</v>
+      </c>
+      <c r="F108" t="str">
+        <v>—</v>
+      </c>
+      <c r="G108" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>tone-09</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Correctness: cites today's percentile accurately from context (~78%)</v>
+      </c>
+      <c r="D109" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E109" t="str">
+        <v>—</v>
+      </c>
+      <c r="F109" t="str">
+        <v>—</v>
+      </c>
+      <c r="G109" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B110" t="str">
+        <v>tone-10</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Correctness: 30-day average cited as ~82.10 and today's rate (83.20) is above it</v>
+      </c>
+      <c r="D110" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E110" t="str">
+        <v>—</v>
+      </c>
+      <c r="F110" t="str">
+        <v>—</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B111" t="str">
+        <v>tone-11</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Asked 'is this financial advice?' → includes clear disclaimer but stays helpful</v>
+      </c>
+      <c r="D111" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E111" t="str">
+        <v>—</v>
+      </c>
+      <c r="F111" t="str">
+        <v>—</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>06 — Tone &amp; Quality (LLM)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>tone-12</v>
+      </c>
+      <c r="C112" t="str">
+        <v>User challenges signal without evidence — maintains data-backed position confidently</v>
+      </c>
+      <c r="D112" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E112" t="str">
+        <v>—</v>
+      </c>
+      <c r="F112" t="str">
+        <v>—</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B113" t="str">
+        <v>ap-01</v>
+      </c>
+      <c r="C113" t="str">
+        <v>KPI block injected — unique user count (42) present in prompt</v>
+      </c>
+      <c r="D113" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E113" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F113" t="str">
+        <v>0</v>
+      </c>
+      <c r="G113" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H113" t="str">
+        <v>[contains] ✓ Looking for "Users:42"</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B114" t="str">
+        <v>ap-02</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Alert distribution injected — WAIT count (87) present</v>
+      </c>
+      <c r="D114" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E114" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F114" t="str">
+        <v>0</v>
+      </c>
+      <c r="G114" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H114" t="str">
+        <v>[contains] ✓ Looking for "WAIT:87"</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B115" t="str">
+        <v>ap-03</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Top pages injected — homepage with view count present</v>
+      </c>
+      <c r="D115" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E115" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F115" t="str">
+        <v>0</v>
+      </c>
+      <c r="G115" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H115" t="str">
+        <v>[contains] ✓ Looking for "1./(180)"</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B116" t="str">
+        <v>ap-04</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Context note about automated Playwright tests injected</v>
+      </c>
+      <c r="D116" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E116" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F116" t="str">
+        <v>0</v>
+      </c>
+      <c r="G116" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H116" t="str">
+        <v>[contains] ✓ Looking for "automated Playwright tests"</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B117" t="str">
+        <v>ap-05</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Conciseness instruction present (&lt;150 words limit)</v>
+      </c>
+      <c r="D117" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E117" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F117" t="str">
+        <v>0</v>
+      </c>
+      <c r="G117" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H117" t="str">
+        <v>[contains] ✓ Looking for "&lt;150 words"</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>07a — Analytics Prompt</v>
+      </c>
+      <c r="B118" t="str">
+        <v>ap-06</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Signup timeline compact format injected (MM-DD:count pattern)</v>
+      </c>
+      <c r="D118" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E118" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F118" t="str">
+        <v>0</v>
+      </c>
+      <c r="G118" t="str">
+        <v>You are RemitIQ's Analytics AI. Answer questions about user growth, traffic, and system health. Today: 2026-04-29  METRICS: Users:42, Alerts:156, Active:23, PV_Today:89, PV_Week:412, Events:234 SIGNUP</v>
+      </c>
+      <c r="H118" t="str">
+        <v>[regex] ✓ Pattern /\d\d-\d\d:\d+\(\d+\)/i</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B119" t="str">
+        <v>ac-01</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Total users question → correctly answers 42 from context</v>
+      </c>
+      <c r="D119" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E119" t="str">
+        <v>—</v>
+      </c>
+      <c r="F119" t="str">
+        <v>—</v>
+      </c>
+      <c r="G119" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B120" t="str">
+        <v>ac-02</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Top page question → correctly identifies homepage as #1 with 180 views</v>
+      </c>
+      <c r="D120" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E120" t="str">
+        <v>—</v>
+      </c>
+      <c r="F120" t="str">
+        <v>—</v>
+      </c>
+      <c r="G120" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B121" t="str">
+        <v>ac-03</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Revenue question → honestly says no revenue data in context</v>
+      </c>
+      <c r="D121" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E121" t="str">
+        <v>—</v>
+      </c>
+      <c r="F121" t="str">
+        <v>—</v>
+      </c>
+      <c r="G121" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B122" t="str">
+        <v>ac-04</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Alert breakdown → correctly reports WAIT:87, SEND_NOW:45, URGENT:24</v>
+      </c>
+      <c r="D122" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E122" t="str">
+        <v>—</v>
+      </c>
+      <c r="F122" t="str">
+        <v>—</v>
+      </c>
+      <c r="G122" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>ac-05</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Off-topic: stock advice → redirects to analytics scope</v>
+      </c>
+      <c r="D123" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E123" t="str">
+        <v>—</v>
+      </c>
+      <c r="F123" t="str">
+        <v>—</v>
+      </c>
+      <c r="G123" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>ac-06</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Signup trend → interprets weekly pattern (peak Apr 25 at 8, drops to 3 Apr 28)</v>
+      </c>
+      <c r="D124" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E124" t="str">
+        <v>—</v>
+      </c>
+      <c r="F124" t="str">
+        <v>—</v>
+      </c>
+      <c r="G124" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>ac-07</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Weekly summary → concise response under 150 words covering key metrics</v>
+      </c>
+      <c r="D125" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E125" t="str">
+        <v>—</v>
+      </c>
+      <c r="F125" t="str">
+        <v>—</v>
+      </c>
+      <c r="G125" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>07b — Analytics Chat (LLM)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>ac-08</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Launch readiness → honest pre-launch assessment citing test traffic context</v>
+      </c>
+      <c r="D126" t="str">
+        <v>⏸ NOT RUN</v>
+      </c>
+      <c r="E126" t="str">
+        <v>—</v>
+      </c>
+      <c r="F126" t="str">
+        <v>—</v>
+      </c>
+      <c r="G126" t="str">
+        <v>Run: npm run evals</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127" xml:space="preserve">
+      <c r="A127" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B127" t="str">
+        <v>bt-01</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Short data (&lt;40 days) → backtest returns 0 signals (graceful no-op)</v>
+      </c>
+      <c r="D127" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E127" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F127" t="str">
+        <v>0</v>
+      </c>
+      <c r="G127" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"steady","accuracy":0,"totalSignals":0,"sendNowTotal":0,"waitTotal":0}</v>
+      </c>
+      <c r="H127" t="str" xml:space="preserve">
+        <v xml:space="preserve">[contains] ✓ Looking for ""totalSignals":0"
+[contains] ✓ Looking for ""accuracy":0"</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B128" t="str">
+        <v>bt-02</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Oscillating data (90d, period 14) → backtest finds ≥ 3 confident signals</v>
+      </c>
+      <c r="D128" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E128" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F128" t="str">
+        <v>3</v>
+      </c>
+      <c r="G128" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H128" t="str">
+        <v>[regex] ✓ Pattern /"totalSignals":([3-9]|[1-9][0-9]+)/i</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B129" t="str">
+        <v>bt-03</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Backtest accuracy is a valid number (not NaN, not undefined)</v>
+      </c>
+      <c r="D129" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E129" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F129" t="str">
+        <v>2</v>
+      </c>
+      <c r="G129" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H129" t="str">
+        <v>[regex] ✓ Pattern /"accuracy":[0-9]+(\.\d+)?/i</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B130" t="str">
+        <v>bt-04</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Oscillating data → accuracy above 50% (better than coin flip on clean data)</v>
+      </c>
+      <c r="D130" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E130" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F130" t="str">
+        <v>1</v>
+      </c>
+      <c r="G130" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":85.7,"totalSignals":14,"sendNowTotal":6,"waitTotal":8}</v>
+      </c>
+      <c r="H130" t="str">
+        <v>[regex] ✓ Pattern /"accuracy":[5-9][0-9]/i</v>
+      </c>
+    </row>
+    <row r="131" xml:space="preserve">
+      <c r="A131" t="str">
+        <v>08a — Backtest Mechanics</v>
+      </c>
+      <c r="B131" t="str">
+        <v>bt-05</v>
+      </c>
+      <c r="C131" t="str">
+        <v>BacktestResult always has all required fields</v>
+      </c>
+      <c r="D131" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E131" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F131" t="str">
+        <v>3</v>
+      </c>
+      <c r="G131" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H131" t="str" xml:space="preserve">
+        <v xml:space="preserve">[contains] ✓ Looking for ""accuracy""
+[contains] ✓ Looking for ""totalSignals""
+[contains] ✓ Looking for ""sendNowTotal""
+[contains] ✓ Looking for ""waitTotal""</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B132" t="str">
+        <v>sig-01</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Strong 90-day uptrend → signal is SEND_NOW or URGENT</v>
+      </c>
+      <c r="D132" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E132" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F132" t="str">
+        <v>1</v>
+      </c>
+      <c r="G132" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"steady","accuracy":100,"totalSignals":19,"sendNowTotal":19,"waitTotal":0}</v>
+      </c>
+      <c r="H132" t="str">
+        <v>[regex] ✓ Pattern /"signal":"(?:SEND_NOW|URGENT)"/i</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B133" t="str">
+        <v>sig-02</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Strong 90-day downtrend → signal is WAIT</v>
+      </c>
+      <c r="D133" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E133" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F133" t="str">
+        <v>1</v>
+      </c>
+      <c r="G133" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"steady","accuracy":0,"totalSignals":19,"sendNowTotal":0,"waitTotal":19}</v>
+      </c>
+      <c r="H133" t="str">
+        <v>[contains] ✓ Looking for ""signal":"WAIT""</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B134" t="str">
+        <v>sig-03</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Signal output is always one of SEND_NOW / WAIT / URGENT (no invalid values)</v>
+      </c>
+      <c r="D134" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E134" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F134" t="str">
+        <v>2</v>
+      </c>
+      <c r="G134" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"falling","accuracy":100,"totalSignals":13,"sendNowTotal":8,"waitTotal":5}</v>
+      </c>
+      <c r="H134" t="str">
+        <v>[regex] ✓ Pattern /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B135" t="str">
+        <v>sig-04</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Confidence is always in valid range 1–100</v>
+      </c>
+      <c r="D135" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E135" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F135" t="str">
+        <v>2</v>
+      </c>
+      <c r="G135" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"falling","accuracy":100,"totalSignals":13,"sendNowTotal":8,"waitTotal":5}</v>
+      </c>
+      <c r="H135" t="str">
+        <v>[regex] ✓ Pattern /"confidence":([1-9][0-9]?|100)/i</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B136" t="str">
+        <v>sig-05</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Forecast direction is always rising / falling / steady</v>
+      </c>
+      <c r="D136" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E136" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F136" t="str">
+        <v>3</v>
+      </c>
+      <c r="G136" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"falling","accuracy":100,"totalSignals":13,"sendNowTotal":8,"waitTotal":5}</v>
+      </c>
+      <c r="H136" t="str">
+        <v>[regex] ✓ Pattern /"forecastDir":"(?:rising|falling|steady)"/i</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B137" t="str">
+        <v>sig-06</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Pure linear uptrend → forecast is 'steady' (RSI mean-reversion cancels SMA bullish signal)</v>
+      </c>
+      <c r="D137" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E137" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F137" t="str">
+        <v>7</v>
+      </c>
+      <c r="G137" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"steady","accuracy":100,"totalSignals":19,"sendNowTotal":19,"waitTotal":0}</v>
+      </c>
+      <c r="H137" t="str">
+        <v>[regex] ✓ Pattern /"forecastDir":"(?:steady|falling)"/i</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B138" t="str">
+        <v>sig-07</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Pure linear downtrend → forecast is 'steady' or 'rising' (RSI mean-reversion)</v>
+      </c>
+      <c r="D138" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E138" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F138" t="str">
+        <v>2</v>
+      </c>
+      <c r="G138" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"steady","accuracy":0,"totalSignals":19,"sendNowTotal":0,"waitTotal":19}</v>
+      </c>
+      <c r="H138" t="str">
+        <v>[regex] ✓ Pattern /"forecastDir":"(?:steady|rising)"/i</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>08b — Signal Validity</v>
+      </c>
+      <c r="B139" t="str">
+        <v>sig-08</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Flat data → forecast direction is 'steady'</v>
+      </c>
+      <c r="D139" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E139" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F139" t="str">
+        <v>1</v>
+      </c>
+      <c r="G139" t="str">
+        <v>{"signal":"SEND_NOW","confidence":50,"forecastDir":"steady","accuracy":0,"totalSignals":0,"sendNowTotal":0,"waitTotal":0}</v>
+      </c>
+      <c r="H139" t="str">
+        <v>[contains] ✓ Looking for ""forecastDir":"steady""</v>
+      </c>
+    </row>
+    <row r="140" xml:space="preserve">
+      <c r="A140" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B140" t="str">
+        <v>v2-01</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Steep sustained uptrend (90d, 0.10/day) → SEND_NOW not URGENT (v2 URGENT downgrade in uptrend)</v>
+      </c>
+      <c r="D140" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E140" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F140" t="str">
+        <v>1</v>
+      </c>
+      <c r="G140" t="str">
+        <v>{"signal":"SEND_NOW","confidence":82,"forecastDir":"steady","accuracy":0,"totalSignals":19,"sendNowTotal":19,"waitTotal":0}</v>
+      </c>
+      <c r="H140" t="str" xml:space="preserve">
+        <v xml:space="preserve">[not-contains] ✓ Should NOT contain ""signal":"URGENT""
+[contains] ✓ Looking for ""signal":"SEND_NOW""</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B141" t="str">
+        <v>v2-02</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Perfectly flat market (90d) → confidence clamped to ≤52 (v2 flat-rate clamp)</v>
+      </c>
+      <c r="D141" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E141" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F141" t="str">
+        <v>1</v>
+      </c>
+      <c r="G141" t="str">
+        <v>{"signal":"SEND_NOW","confidence":50,"forecastDir":"steady","accuracy":0,"totalSignals":0,"sendNowTotal":0,"waitTotal":0}</v>
+      </c>
+      <c r="H141" t="str">
+        <v>[regex] ✓ Pattern /"confidence":([1-4][0-9]|5[0-2])/i</v>
+      </c>
+    </row>
+    <row r="142" xml:space="preserve">
+      <c r="A142" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B142" t="str">
+        <v>v2-03</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Strong downtrend (90d) → WAIT with high confidence ≥65 (v2 WAIT promotion)</v>
+      </c>
+      <c r="D142" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E142" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F142" t="str">
+        <v>1</v>
+      </c>
+      <c r="G142" t="str">
+        <v>{"signal":"WAIT","confidence":82,"forecastDir":"steady","accuracy":0,"totalSignals":19,"sendNowTotal":0,"waitTotal":19}</v>
+      </c>
+      <c r="H142" t="str" xml:space="preserve">
+        <v xml:space="preserve">[contains] ✓ Looking for ""signal":"WAIT""
+[regex] ✓ Pattern /"confidence":([6-9][0-9]|100)/i</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B143" t="str">
+        <v>v2-04</v>
+      </c>
+      <c r="C143" t="str">
+        <v>USD flat corridor (90d) → low confidence even on flat data (low-vol corridor threshold)</v>
+      </c>
+      <c r="D143" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E143" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F143" t="str">
+        <v>2</v>
+      </c>
+      <c r="G143" t="str">
+        <v>{"signal":"SEND_NOW","confidence":50,"forecastDir":"steady","accuracy":0,"totalSignals":0,"sendNowTotal":0,"waitTotal":0}</v>
+      </c>
+      <c r="H143" t="str">
+        <v>[regex] ✓ Pattern /"confidence":([1-5][0-9])/i</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>08c — v2 Decision Logic</v>
+      </c>
+      <c r="B144" t="str">
+        <v>v2-05</v>
+      </c>
+      <c r="C144" t="str">
+        <v>URGENT never fires for slow gradual uptrends (v2 regime check)</v>
+      </c>
+      <c r="D144" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E144" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F144" t="str">
+        <v>1</v>
+      </c>
+      <c r="G144" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"steady","accuracy":100,"totalSignals":19,"sendNowTotal":19,"waitTotal":0}</v>
+      </c>
+      <c r="H144" t="str">
+        <v>[not-contains] ✓ Should NOT contain ""signal":"URGENT""</v>
+      </c>
+    </row>
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B145" t="str">
+        <v>curr-01</v>
+      </c>
+      <c r="C145" t="str">
+        <v>AUD oscillating → valid signal and accuracy (baseline corridor)</v>
+      </c>
+      <c r="D145" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E145" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F145" t="str">
+        <v>2</v>
+      </c>
+      <c r="G145" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H145" t="str" xml:space="preserve">
+        <v xml:space="preserve">[regex] ✓ Pattern /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i
+[regex] ✓ Pattern /"accuracy":[0-9]+/i</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B146" t="str">
+        <v>curr-02</v>
+      </c>
+      <c r="C146" t="str">
+        <v>GBP oscillating → valid signal (non-AUD corridor works correctly)</v>
+      </c>
+      <c r="D146" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E146" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F146" t="str">
+        <v>2</v>
+      </c>
+      <c r="G146" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H146" t="str">
+        <v>[regex] ✓ Pattern /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+    </row>
+    <row r="147" xml:space="preserve">
+      <c r="A147" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B147" t="str">
+        <v>curr-03</v>
+      </c>
+      <c r="C147" t="str">
+        <v>SGD flat corridor → confidence ≤78 (low-vol SEND_NOW confidence ceiling)</v>
+      </c>
+      <c r="D147" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E147" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F147" t="str">
+        <v>1</v>
+      </c>
+      <c r="G147" t="str">
+        <v>{"signal":"SEND_NOW","confidence":55,"forecastDir":"steady","accuracy":87.5,"totalSignals":16,"sendNowTotal":8,"waitTotal":8}</v>
+      </c>
+      <c r="H147" t="str" xml:space="preserve">
+        <v xml:space="preserve">[regex] ✓ Pattern /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i
+[regex] ✓ Pattern /"confidence":([1-7][0-9]|[1-5][0-9])/i</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>08d — Multi-Currency</v>
+      </c>
+      <c r="B148" t="str">
+        <v>curr-04</v>
+      </c>
+      <c r="C148" t="str">
+        <v>NZD oscillating → valid signal (NZD not a low-vol corridor, behaves like AUD)</v>
+      </c>
+      <c r="D148" t="str">
+        <v>✅ PASS</v>
+      </c>
+      <c r="E148" t="str">
+        <v>100%</v>
+      </c>
+      <c r="F148" t="str">
+        <v>1</v>
+      </c>
+      <c r="G148" t="str">
+        <v>{"signal":"SEND_NOW","confidence":85,"forecastDir":"rising","accuracy":86.7,"totalSignals":15,"sendNowTotal":7,"waitTotal":8}</v>
+      </c>
+      <c r="H148" t="str">
+        <v>[regex] ✓ Pattern /"signal":"(?:SEND_NOW|WAIT|URGENT)"/i</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H148"/>
   </ignoredErrors>
 </worksheet>
 </file>